--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251023_201442.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251023_201442.xlsx
@@ -5230,7 +5230,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251023_201442.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251023_201442.xlsx
@@ -5230,7 +5230,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251023_201442.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251023_201442.xlsx
@@ -5230,7 +5230,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251023_201442.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251023_201442.xlsx
@@ -7232,7 +7232,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251023_201442.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251023_201442.xlsx
@@ -7232,7 +7232,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251023_201442.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251023_201442.xlsx
@@ -5230,7 +5230,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
